--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="96">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>Level</t>
@@ -162,10 +162,13 @@
     <t>Door to Groin &lt;= 120 Minutes</t>
   </si>
   <si>
+    <t>D2D</t>
+  </si>
+  <si>
+    <t>Door to Door</t>
+  </si>
+  <si>
     <t>Door2Door</t>
-  </si>
-  <si>
-    <t>Door to Door</t>
   </si>
   <si>
     <t>Door2Discharge</t>
@@ -607,7 +610,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -692,7 +695,7 @@
         <v>51</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -701,10 +704,10 @@
         <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>54</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -713,10 +716,10 @@
         <v>40</v>
       </c>
       <c r="B9" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s" s="2">
         <v>55</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>56</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -725,10 +728,10 @@
         <v>40</v>
       </c>
       <c r="B10" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -737,10 +740,10 @@
         <v>40</v>
       </c>
       <c r="B11" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>60</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -749,10 +752,10 @@
         <v>40</v>
       </c>
       <c r="B12" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -761,10 +764,10 @@
         <v>40</v>
       </c>
       <c r="B13" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>64</v>
       </c>
       <c r="D13" s="2"/>
     </row>
@@ -773,10 +776,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s" s="2">
         <v>65</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>66</v>
       </c>
       <c r="D14" s="2"/>
     </row>
@@ -785,10 +788,10 @@
         <v>40</v>
       </c>
       <c r="B15" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>67</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>68</v>
       </c>
       <c r="D15" s="2"/>
     </row>
@@ -797,10 +800,10 @@
         <v>40</v>
       </c>
       <c r="B16" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>69</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>70</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -809,10 +812,10 @@
         <v>40</v>
       </c>
       <c r="B17" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="D17" s="2"/>
     </row>
@@ -821,10 +824,10 @@
         <v>40</v>
       </c>
       <c r="B18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>74</v>
       </c>
       <c r="D18" s="2"/>
     </row>
@@ -833,10 +836,10 @@
         <v>40</v>
       </c>
       <c r="B19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="D19" s="2"/>
     </row>
@@ -845,10 +848,10 @@
         <v>40</v>
       </c>
       <c r="B20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>77</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="D20" s="2"/>
     </row>
@@ -857,10 +860,10 @@
         <v>40</v>
       </c>
       <c r="B21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>79</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -869,10 +872,10 @@
         <v>40</v>
       </c>
       <c r="B22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="D22" s="2"/>
     </row>
@@ -881,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="B23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="D23" s="2"/>
     </row>
@@ -893,10 +896,10 @@
         <v>40</v>
       </c>
       <c r="B24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="D24" s="2"/>
     </row>
@@ -905,10 +908,10 @@
         <v>40</v>
       </c>
       <c r="B25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="D25" s="2"/>
     </row>
@@ -917,10 +920,10 @@
         <v>40</v>
       </c>
       <c r="B26" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="D26" s="2"/>
     </row>
@@ -929,10 +932,10 @@
         <v>40</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="D27" s="2"/>
     </row>
@@ -941,12 +944,24 @@
         <v>40</v>
       </c>
       <c r="B28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="C28" t="s" s="2">
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="D28" s="2"/>
+      <c r="C29" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="D29" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
